--- a/49841_Intercuenca_Bajo_Huallaga/_raw_reportes_xlsx/IDConfig_65281_completo.xlsx
+++ b/49841_Intercuenca_Bajo_Huallaga/_raw_reportes_xlsx/IDConfig_65281_completo.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R05bd7feb9ee24f4c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R9ae3ca8324874a1e"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -255,6 +255,141 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
+          <x:t>23/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    111.8702</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    111.8477</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    111.6452</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    111.5077</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    111.6102</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    111.8552</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    112.0777</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    112.3652</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    112.4677</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
           <x:t>14/08/2026</x:t>
         </x:is>
       </x:c>

--- a/49841_Intercuenca_Bajo_Huallaga/_raw_reportes_xlsx/IDConfig_65281_completo.xlsx
+++ b/49841_Intercuenca_Bajo_Huallaga/_raw_reportes_xlsx/IDConfig_65281_completo.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R9ae3ca8324874a1e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R2708458d7dad4dfd"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -255,6 +255,726 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
+          <x:t>10/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    111.0402</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    111.2152</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    111.5352</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    111.8202</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    112.0727</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    111.7277</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    111.6377</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    111.6402</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    111.8102</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    111.9027</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    111.7452</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    111.3877</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    111.3752</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    111.4252</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    111.4402</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    111.6152</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    111.9727</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    112.4077</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    112.5952</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    112.3977</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    112.3952</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    112.4377</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    112.4077</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    112.0002</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    111.1027</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    110.9102</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>14/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    111.0527</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>13/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    111.1252</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>12/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    111.0927</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>11/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    111.0277</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    110.9002</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    110.8902</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    110.9177</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    110.9877</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    111.0402</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    111.0402</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    111.1352</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    111.3527</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    111.6102</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    111.9777</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>31/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    112.4177</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    112.8402</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    113.0502</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    112.8752</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    112.3677</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    111.9027</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    111.7152</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    111.8752</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
           <x:t>23/08/2026</x:t>
         </x:is>
       </x:c>
